--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.36434383935517</v>
+        <v>8.346705873895216</v>
       </c>
       <c r="D2" t="n">
-        <v>50.13427948981722</v>
+        <v>8.146820417095299</v>
       </c>
       <c r="E2" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F2" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>34.78388134806624</v>
+        <v>5.652380719060764</v>
       </c>
       <c r="D3" t="n">
-        <v>34.90368754852921</v>
+        <v>5.671849226635996</v>
       </c>
       <c r="E3" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F3" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>26.62978455360405</v>
+        <v>4.327339989960659</v>
       </c>
       <c r="D4" t="n">
-        <v>25.83121639609336</v>
+        <v>4.197572664365172</v>
       </c>
       <c r="E4" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F4" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.154347323288901</v>
+        <v>1.325081440034446</v>
       </c>
       <c r="D5" t="n">
-        <v>7.443241350869294</v>
+        <v>1.20952671951626</v>
       </c>
       <c r="E5" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F5" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.40045241811274</v>
+        <v>3.477573517943321</v>
       </c>
       <c r="D6" t="n">
-        <v>21.93420237119394</v>
+        <v>3.564307885319016</v>
       </c>
       <c r="E6" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F6" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.89929468105147</v>
+        <v>3.883635385670865</v>
       </c>
       <c r="D7" t="n">
-        <v>31.2779127294849</v>
+        <v>5.082660818541297</v>
       </c>
       <c r="E7" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F7" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>18.70518695988869</v>
+        <v>3.039592880981911</v>
       </c>
       <c r="D8" t="n">
-        <v>29.13755674274518</v>
+        <v>4.734852970696092</v>
       </c>
       <c r="E8" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F8" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5.639678884910163</v>
+        <v>0.9164478187979015</v>
       </c>
       <c r="D9" t="n">
-        <v>29.90539448253341</v>
+        <v>4.859626603411678</v>
       </c>
       <c r="E9" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F9" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.69360234550339</v>
+        <v>7.587710381144301</v>
       </c>
       <c r="D10" t="n">
-        <v>54.67003292481174</v>
+        <v>8.883880350281908</v>
       </c>
       <c r="E10" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F10" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>6.297761267479688</v>
+        <v>1.023386205965449</v>
       </c>
       <c r="D11" t="n">
-        <v>38.23931955801682</v>
+        <v>6.213889428177733</v>
       </c>
       <c r="E11" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F11" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>52.08771751095153</v>
+        <v>8.464254095529624</v>
       </c>
       <c r="D12" t="n">
-        <v>67.62172512963828</v>
+        <v>10.98853033356622</v>
       </c>
       <c r="E12" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F12" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.35521318824752</v>
+        <v>3.470222143090222</v>
       </c>
       <c r="D13" t="n">
-        <v>51.87314739384549</v>
+        <v>8.429386451499893</v>
       </c>
       <c r="E13" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F13" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>62.40520804430366</v>
+        <v>10.14084630719934</v>
       </c>
       <c r="D14" t="n">
-        <v>84.7260982420825</v>
+        <v>13.76799096433841</v>
       </c>
       <c r="E14" t="n">
-        <v>18.06959586028142</v>
+        <v>2.93630932729573</v>
       </c>
       <c r="F14" t="n">
-        <v>19.8645827883836</v>
+        <v>3.227994703112335</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
